--- a/QFD_Lunar_Gateway_Supply_Chain.xlsx
+++ b/QFD_Lunar_Gateway_Supply_Chain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prasannakumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{999E6AA6-8900-FE49-8639-41160523379D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2208BC32-D626-F24A-9410-E36CB47DDAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
